--- a/artfynd/A 22085-2026 artfynd.xlsx
+++ b/artfynd/A 22085-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128427404</v>
+        <v>128606301</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>56814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,53 +686,58 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Ledningsgatan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546998</v>
+        <v>547184</v>
       </c>
       <c r="R2" t="n">
-        <v>6323474</v>
+        <v>6323479</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +761,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,10 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128427387</v>
+        <v>128606318</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>56827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,53 +819,58 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100087</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Ledningsgatan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547064</v>
+        <v>547184</v>
       </c>
       <c r="R3" t="n">
-        <v>6323460</v>
+        <v>6323479</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +894,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,64 +941,69 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128427375</v>
+        <v>128606329</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>56830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+          <t>Ledningsgatan, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547103</v>
+        <v>547184</v>
       </c>
       <c r="R4" t="n">
-        <v>6323490</v>
+        <v>6323479</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,22 +1027,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,6 +1071,641 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128427375</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>547103</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6323490</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128427387</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>547064</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6323460</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128427404</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>546998</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6323474</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128606326</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ledningsgatan, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>547184</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6323479</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128606312</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ledningsgatan, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>547184</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6323479</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22085-2026 artfynd.xlsx
+++ b/artfynd/A 22085-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128606301</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -938,6 +948,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128606318</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1071,6 +1086,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128606329</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1194,6 +1214,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128427375</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1317,6 +1342,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128427387</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1440,6 +1470,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128427404</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1573,6 +1608,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128606326</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1706,8 +1746,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128606312</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>